--- a/04_Figures/F04_association/modules/total/spearman/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/total/spearman/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0153846153846154</v>
+        <v>-0.151648351648352</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0533001790889026</v>
+        <v>-0.531472035224587</v>
       </c>
       <c r="F2" t="n">
-        <v>0.958369789371986</v>
+        <v>0.604790598452137</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9940505286659</v>
+        <v>0.890614350979531</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.226373626373626</v>
+        <v>-0.0637362637362637</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.80508070183143</v>
+        <v>-0.221238721732763</v>
       </c>
       <c r="F3" t="n">
-        <v>0.436434794556053</v>
+        <v>0.828626422928612</v>
       </c>
       <c r="G3" t="n">
-        <v>0.879874983575368</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.375824175824176</v>
+        <v>-0.38021978021978</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.40488377474981</v>
+        <v>-1.42407332037068</v>
       </c>
       <c r="F4" t="n">
-        <v>0.185410028697123</v>
+        <v>0.179906146306081</v>
       </c>
       <c r="G4" t="n">
-        <v>0.879874983575368</v>
+        <v>0.816987706248283</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.120879120879121</v>
+        <v>0.283516483516484</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.421830743866054</v>
+        <v>1.0241536325576</v>
       </c>
       <c r="F5" t="n">
-        <v>0.680607020062893</v>
+        <v>0.325965947441773</v>
       </c>
       <c r="G5" t="n">
-        <v>0.983099028979734</v>
+        <v>0.816987706248283</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0021978021978022</v>
+        <v>-0.0153846153846154</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00761342853088536</v>
+        <v>-0.0533001790889026</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9940505286659</v>
+        <v>0.958369789371986</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9940505286659</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.345054945054945</v>
+        <v>0.0417582417582418</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.27352194297108</v>
+        <v>0.144781078854707</v>
       </c>
       <c r="F7" t="n">
-        <v>0.226948680041701</v>
+        <v>0.887286973189064</v>
       </c>
       <c r="G7" t="n">
-        <v>0.879874983575368</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0373626373626374</v>
+        <v>0.468131868131868</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12951840569399</v>
+        <v>1.83516159583906</v>
       </c>
       <c r="F8" t="n">
-        <v>0.899093096973967</v>
+        <v>0.0913763650683312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9940505286659</v>
+        <v>0.816987706248283</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.534065934065934</v>
+        <v>-0.134065934065934</v>
       </c>
       <c r="E9" t="n">
-        <v>2.18827175544225</v>
+        <v>-0.468648785948378</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0491599163719851</v>
+        <v>0.647719527985113</v>
       </c>
       <c r="G9" t="n">
-        <v>0.639078912835806</v>
+        <v>0.890614350979531</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.287912087912088</v>
+        <v>-0.248351648351648</v>
       </c>
       <c r="E10" t="n">
-        <v>1.04145523072203</v>
+        <v>-0.888140849482722</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3181928710258</v>
+        <v>0.391919538938457</v>
       </c>
       <c r="G10" t="n">
-        <v>0.879874983575368</v>
+        <v>0.816987706248283</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.208791208791209</v>
+        <v>0.221978021978022</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.739573996953447</v>
+        <v>0.788629411844184</v>
       </c>
       <c r="F11" t="n">
-        <v>0.473778837309814</v>
+        <v>0.445629657953609</v>
       </c>
       <c r="G11" t="n">
-        <v>0.879874983575368</v>
+        <v>0.816987706248283</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0153846153846154</v>
+        <v>-0.305494505494505</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0533001790889026</v>
+        <v>-1.11139556517412</v>
       </c>
       <c r="F12" t="n">
-        <v>0.958369789371986</v>
+        <v>0.288169885875457</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9940505286659</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.23956043956044</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.854750807147626</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.409429892851733</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.879874983575368</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.164835164835165</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.578924798693409</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.573346405013138</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.93168790814635</v>
+        <v>0.816987706248283</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.134065934065934</v>
+        <v>0.0549450549450549</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.468648785948378</v>
+        <v>0.190623212915756</v>
       </c>
       <c r="F2" t="n">
-        <v>0.647719527985113</v>
+        <v>0.852007703632368</v>
       </c>
       <c r="G2" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0857142857142857</v>
+        <v>-0.217582417582418</v>
       </c>
       <c r="E3" t="n">
-        <v>0.298019780339635</v>
+        <v>-0.772228696551556</v>
       </c>
       <c r="F3" t="n">
-        <v>0.770785031118676</v>
+        <v>0.454919373170033</v>
       </c>
       <c r="G3" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.134065934065934</v>
+        <v>-0.0461538461538462</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.468648785948378</v>
+        <v>-0.160052173656655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.647719527985113</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G4" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.323076923076923</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.18259041285079</v>
+        <v>0.821583836257749</v>
       </c>
       <c r="F5" t="n">
-        <v>0.25987361950879</v>
+        <v>0.42733586167745</v>
       </c>
       <c r="G5" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0813186813186813</v>
+        <v>0.0549450549450549</v>
       </c>
       <c r="E6" t="n">
-        <v>0.282632210255267</v>
+        <v>0.190623212915756</v>
       </c>
       <c r="F6" t="n">
-        <v>0.782274751244096</v>
+        <v>0.852007703632368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0945054945054945</v>
+        <v>-0.125274725274725</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.328848450013655</v>
+        <v>-0.437410256409312</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747938261141548</v>
+        <v>0.669582396544844</v>
       </c>
       <c r="G7" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0857142857142857</v>
+        <v>0.340659340659341</v>
       </c>
       <c r="E8" t="n">
-        <v>0.298019780339635</v>
+        <v>1.25515331177732</v>
       </c>
       <c r="F8" t="n">
-        <v>0.770785031118676</v>
+        <v>0.233316051036824</v>
       </c>
       <c r="G8" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.393406593406593</v>
+        <v>-0.0461538461538462</v>
       </c>
       <c r="E9" t="n">
-        <v>1.48232858660886</v>
+        <v>-0.160052173656655</v>
       </c>
       <c r="F9" t="n">
-        <v>0.164031573400778</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G9" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.235164835164835</v>
+        <v>-0.125274725274725</v>
       </c>
       <c r="E10" t="n">
-        <v>0.838140102702703</v>
+        <v>-0.437410256409312</v>
       </c>
       <c r="F10" t="n">
-        <v>0.418333896198592</v>
+        <v>0.669582396544844</v>
       </c>
       <c r="G10" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.147252747252747</v>
+        <v>-0.032967032967033</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.515720400699903</v>
+        <v>-0.114263261126781</v>
       </c>
       <c r="F11" t="n">
-        <v>0.615418762484725</v>
+        <v>0.910918653071845</v>
       </c>
       <c r="G11" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0461538461538462</v>
+        <v>-0.0769230769230769</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.160052173656655</v>
+        <v>-0.267261241912424</v>
       </c>
       <c r="F12" t="n">
-        <v>0.875502537632114</v>
+        <v>0.793805888355453</v>
       </c>
       <c r="G12" t="n">
-        <v>0.934618994603643</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0241758241758242</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0837719962821407</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.934618994603643</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.934618994603643</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.103296703296703</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.359754753325688</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.725282211088945</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.924506524197568</v>
+        <v>0.910918653071845</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.195604395604396</v>
+        <v>-0.0593406593406593</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.690940479624547</v>
+        <v>-0.20592495680455</v>
       </c>
       <c r="F2" t="n">
-        <v>0.502750091296957</v>
+        <v>0.840301762690683</v>
       </c>
       <c r="G2" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0285714285714286</v>
+        <v>-0.16043956043956</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0990147542976674</v>
+        <v>-0.563073178275514</v>
       </c>
       <c r="F3" t="n">
-        <v>0.922761376569875</v>
+        <v>0.583752752641341</v>
       </c>
       <c r="G3" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.125274725274725</v>
+        <v>-0.0725274725274725</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.437410256409312</v>
+        <v>-0.251905950462024</v>
       </c>
       <c r="F4" t="n">
-        <v>0.669582396544844</v>
+        <v>0.805376313541092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.226373626373626</v>
+        <v>0.41978021978022</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.80508070183143</v>
+        <v>1.60215956847611</v>
       </c>
       <c r="F5" t="n">
-        <v>0.436434794556053</v>
+        <v>0.135101073829143</v>
       </c>
       <c r="G5" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0989010989010989</v>
+        <v>0.0681318681318681</v>
       </c>
       <c r="E6" t="n">
-        <v>0.344291425054203</v>
+        <v>0.236565415689409</v>
       </c>
       <c r="F6" t="n">
-        <v>0.736585369925317</v>
+        <v>0.816983879781792</v>
       </c>
       <c r="G6" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.257142857142857</v>
+        <v>-0.169230769230769</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.92176480169854</v>
+        <v>-0.594811877479463</v>
       </c>
       <c r="F7" t="n">
-        <v>0.37481190387997</v>
+        <v>0.563017273996211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0461538461538462</v>
+        <v>0.305494505494505</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.160052173656655</v>
+        <v>1.11139556517412</v>
       </c>
       <c r="F8" t="n">
-        <v>0.875502537632114</v>
+        <v>0.288169885875457</v>
       </c>
       <c r="G8" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.367032967032967</v>
+        <v>-0.156043956043956</v>
       </c>
       <c r="E9" t="n">
-        <v>1.36683363683457</v>
+        <v>-0.547255944180659</v>
       </c>
       <c r="F9" t="n">
-        <v>0.196738871707488</v>
+        <v>0.594234700580851</v>
       </c>
       <c r="G9" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.410989010989011</v>
+        <v>-0.204395604395604</v>
       </c>
       <c r="E10" t="n">
-        <v>1.56169895075115</v>
+        <v>-0.723317557443421</v>
       </c>
       <c r="F10" t="n">
-        <v>0.144332668124605</v>
+        <v>0.483346223042223</v>
       </c>
       <c r="G10" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.248351648351648</v>
+        <v>0.0549450549450549</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.888140849482722</v>
+        <v>0.190623212915756</v>
       </c>
       <c r="F11" t="n">
-        <v>0.391919538938457</v>
+        <v>0.852007703632368</v>
       </c>
       <c r="G11" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0637362637362637</v>
+        <v>-0.0901098901098901</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.221238721732763</v>
+        <v>-0.313424881933839</v>
       </c>
       <c r="F12" t="n">
-        <v>0.828626422928612</v>
+        <v>0.759338837815954</v>
       </c>
       <c r="G12" t="n">
-        <v>0.922761376569875</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.107692307692308</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.375239387193228</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.714030808726249</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.922761376569875</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.164835164835165</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.578924798693409</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.573346405013138</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.922761376569875</v>
+        <v>0.852007703632368</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.191208791208791</v>
+        <v>-0.116483516483516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.674817478932826</v>
+        <v>-0.406276413480895</v>
       </c>
       <c r="F2" t="n">
-        <v>0.512583970470779</v>
+        <v>0.691691250233157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.813247173550082</v>
+        <v>0.845400416951637</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.389010989010989</v>
+        <v>0.463736263736264</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.46279326565877</v>
+        <v>1.81318054513692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.16921738979769</v>
+        <v>0.0948763315088996</v>
       </c>
       <c r="G3" t="n">
-        <v>0.549956516842494</v>
+        <v>0.260909911649474</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.648351648351648</v>
+        <v>-0.525274725274725</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.95</v>
+        <v>-2.13836537292849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0121442225731057</v>
+        <v>0.053747501767883</v>
       </c>
       <c r="G4" t="n">
-        <v>0.157874893450374</v>
+        <v>0.260909911649474</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.494505494505494</v>
+        <v>-0.0241758241758242</v>
       </c>
       <c r="E5" t="n">
-        <v>1.97085542334902</v>
+        <v>-0.0837719962821407</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0722496740341326</v>
+        <v>0.934618994603643</v>
       </c>
       <c r="G5" t="n">
-        <v>0.313081920814575</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.265934065934066</v>
+        <v>-0.23956043956044</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.955633835704927</v>
+        <v>-0.854750807147626</v>
       </c>
       <c r="F6" t="n">
-        <v>0.358113400364786</v>
+        <v>0.409429892851733</v>
       </c>
       <c r="G6" t="n">
-        <v>0.665067743534603</v>
+        <v>0.750621470228176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.12967032967033</v>
+        <v>0.243956043956044</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.453015938607022</v>
+        <v>0.871417274558076</v>
       </c>
       <c r="F7" t="n">
-        <v>0.658619276321178</v>
+        <v>0.400624803916119</v>
       </c>
       <c r="G7" t="n">
-        <v>0.856205059217531</v>
+        <v>0.750621470228176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.336263736263736</v>
+        <v>0.485714285714286</v>
       </c>
       <c r="E8" t="n">
-        <v>1.23687779440215</v>
+        <v>1.92487095804581</v>
       </c>
       <c r="F8" t="n">
-        <v>0.239792202257253</v>
+        <v>0.0782758864586334</v>
       </c>
       <c r="G8" t="n">
-        <v>0.623459725868858</v>
+        <v>0.260909911649474</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.507692307692308</v>
+        <v>0.134065934065934</v>
       </c>
       <c r="E9" t="n">
-        <v>2.04134559463475</v>
+        <v>0.468648785948378</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0638391581337686</v>
+        <v>0.647719527985113</v>
       </c>
       <c r="G9" t="n">
-        <v>0.313081920814575</v>
+        <v>0.845400416951637</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.010989010989011</v>
+        <v>0.0153846153846154</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0380693493813441</v>
+        <v>0.0533001790889026</v>
       </c>
       <c r="F10" t="n">
-        <v>0.970258390096969</v>
+        <v>0.958369789371986</v>
       </c>
       <c r="G10" t="n">
-        <v>0.970258390096969</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0549450549450549</v>
+        <v>0.182417582417582</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.190623212915756</v>
+        <v>0.642696755708738</v>
       </c>
       <c r="F11" t="n">
-        <v>0.852007703632368</v>
+        <v>0.532508818518694</v>
       </c>
       <c r="G11" t="n">
-        <v>0.923008345601732</v>
+        <v>0.836799571957948</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.27032967032967</v>
+        <v>-0.626373626373626</v>
       </c>
       <c r="E12" t="n">
-        <v>0.972663845975844</v>
+        <v>-2.78352523225513</v>
       </c>
       <c r="F12" t="n">
-        <v>0.349919386349604</v>
+        <v>0.0165419354288712</v>
       </c>
       <c r="G12" t="n">
-        <v>0.665067743534603</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0681318681318681</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.236565415689409</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.816983879781792</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.923008345601732</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.169230769230769</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.594811877479463</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.563017273996211</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.813247173550082</v>
+        <v>0.181961289717583</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.205300014141822</v>
+        <v>-0.258280662952615</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.726658601750951</v>
+        <v>-0.926134267245632</v>
       </c>
       <c r="F2" t="n">
-        <v>0.481370297098765</v>
+        <v>0.372627515702466</v>
       </c>
       <c r="G2" t="n">
-        <v>0.815913707455199</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.17439463566886</v>
+        <v>0.165564527533728</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.61352245499117</v>
+        <v>0.581558459234465</v>
       </c>
       <c r="F3" t="n">
-        <v>0.550983597252068</v>
+        <v>0.571627105910981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.815913707455199</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.116998932790501</v>
+        <v>0.0331129055067455</v>
       </c>
       <c r="E4" t="n">
-        <v>0.408098999478513</v>
+        <v>0.114769406995615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.69038852169286</v>
+        <v>0.910525922192681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.815913707455199</v>
+        <v>0.94625276368264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.187639797871558</v>
+        <v>0.434882825655258</v>
       </c>
       <c r="E5" t="n">
-        <v>0.661757525478576</v>
+        <v>1.67295942575489</v>
       </c>
       <c r="F5" t="n">
-        <v>0.520631994545967</v>
+        <v>0.120182559331165</v>
       </c>
       <c r="G5" t="n">
-        <v>0.815913707455199</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.156734419398595</v>
+        <v>-0.183224743803992</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.549738288649676</v>
+        <v>-0.64563912207637</v>
       </c>
       <c r="F6" t="n">
-        <v>0.592583253617127</v>
+        <v>0.530665355012191</v>
       </c>
       <c r="G6" t="n">
-        <v>0.815913707455199</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0154526892364812</v>
+        <v>-0.21854517634452</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.053536077946302</v>
+        <v>-0.775816644501819</v>
       </c>
       <c r="F7" t="n">
-        <v>0.958185730270463</v>
+        <v>0.45287661279128</v>
       </c>
       <c r="G7" t="n">
-        <v>0.958185730270463</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.125829040925633</v>
+        <v>-0.187639797871558</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.439376776708006</v>
+        <v>-0.661757525478576</v>
       </c>
       <c r="F8" t="n">
-        <v>0.668196444544155</v>
+        <v>0.520631994545967</v>
       </c>
       <c r="G8" t="n">
-        <v>0.815913707455199</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.156734419398595</v>
+        <v>-0.0551881758445759</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.549738288649676</v>
+        <v>-0.191469253719122</v>
       </c>
       <c r="F9" t="n">
-        <v>0.592583253617127</v>
+        <v>0.851359485875606</v>
       </c>
       <c r="G9" t="n">
-        <v>0.815913707455199</v>
+        <v>0.94625276368264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.430467771587692</v>
+        <v>0.364241960574201</v>
       </c>
       <c r="E10" t="n">
-        <v>1.65208760909287</v>
+        <v>1.35484298188477</v>
       </c>
       <c r="F10" t="n">
-        <v>0.124422212050408</v>
+        <v>0.200425414148861</v>
       </c>
       <c r="G10" t="n">
-        <v>0.815913707455199</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.161149473466161</v>
+        <v>-0.0198677433040473</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.565630941325089</v>
+        <v>-0.0688374690211762</v>
       </c>
       <c r="F11" t="n">
-        <v>0.58206691151376</v>
+        <v>0.94625276368264</v>
       </c>
       <c r="G11" t="n">
-        <v>0.815913707455199</v>
+        <v>0.94625276368264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.116998932790501</v>
+        <v>0.134659149060765</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.408098999478513</v>
+        <v>0.470760673971169</v>
       </c>
       <c r="F12" t="n">
-        <v>0.69038852169286</v>
+        <v>0.646253491004666</v>
       </c>
       <c r="G12" t="n">
-        <v>0.815913707455199</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0816785002499723</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.283891181939403</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.781332631337183</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.846443683948615</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.21854517634452</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.775816644501819</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.45287661279128</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.815913707455199</v>
+        <v>0.888598550131416</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0220386511193563</v>
+        <v>-0.190083365904448</v>
       </c>
       <c r="E2" t="n">
-        <v>0.073111694058163</v>
+        <v>-0.642142780799888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.94302974174218</v>
+        <v>0.533934267666619</v>
       </c>
       <c r="G2" t="n">
-        <v>0.978622775276868</v>
+        <v>0.734159618041601</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.347108755129862</v>
+        <v>0.0578514591883104</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.22755273662222</v>
+        <v>0.192193468966435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.24523667536081</v>
+        <v>0.851092761083698</v>
       </c>
       <c r="G3" t="n">
-        <v>0.79071601712743</v>
+        <v>0.964377780387274</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.212122017023805</v>
+        <v>-0.402205382928253</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.719912042738302</v>
+        <v>-1.4570095764288</v>
       </c>
       <c r="F4" t="n">
-        <v>0.486594472078418</v>
+        <v>0.173060593753027</v>
       </c>
       <c r="G4" t="n">
-        <v>0.79071601712743</v>
+        <v>0.475916632820825</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00826449416975863</v>
+        <v>-0.0137741569495977</v>
       </c>
       <c r="E5" t="n">
-        <v>0.027411162375895</v>
+        <v>-0.0456880447478406</v>
       </c>
       <c r="F5" t="n">
-        <v>0.978622775276868</v>
+        <v>0.964377780387274</v>
       </c>
       <c r="G5" t="n">
-        <v>0.978622775276868</v>
+        <v>0.964377780387274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.250689656482678</v>
+        <v>0.209367185633885</v>
       </c>
       <c r="E6" t="n">
-        <v>0.85886937041153</v>
+        <v>0.710130964267744</v>
       </c>
       <c r="F6" t="n">
-        <v>0.408738785760809</v>
+        <v>0.492403308545325</v>
       </c>
       <c r="G6" t="n">
-        <v>0.79071601712743</v>
+        <v>0.734159618041601</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.305786284281069</v>
+        <v>0.0165289883395173</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.06520132520555</v>
+        <v>0.0548279426993271</v>
       </c>
       <c r="F7" t="n">
-        <v>0.309607819636201</v>
+        <v>0.957258688126924</v>
       </c>
       <c r="G7" t="n">
-        <v>0.79071601712743</v>
+        <v>0.964377780387274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0550966277983909</v>
+        <v>0.418734371267771</v>
       </c>
       <c r="E8" t="n">
-        <v>0.183012833143425</v>
+        <v>1.52931548748664</v>
       </c>
       <c r="F8" t="n">
-        <v>0.858117503842751</v>
+        <v>0.154419887229159</v>
       </c>
       <c r="G8" t="n">
-        <v>0.978622775276868</v>
+        <v>0.475916632820825</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.429753696827449</v>
+        <v>-0.236915499533081</v>
       </c>
       <c r="E9" t="n">
-        <v>1.57853461767748</v>
+        <v>-0.808785738672677</v>
       </c>
       <c r="F9" t="n">
-        <v>0.142747751241424</v>
+        <v>0.435782488285875</v>
       </c>
       <c r="G9" t="n">
-        <v>0.79071601712743</v>
+        <v>0.734159618041601</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.06060629057823</v>
+        <v>-0.512398638525035</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.201378509992724</v>
+        <v>-1.97896774640006</v>
       </c>
       <c r="F10" t="n">
-        <v>0.844078120732535</v>
+        <v>0.0733986917005982</v>
       </c>
       <c r="G10" t="n">
-        <v>0.978622775276868</v>
+        <v>0.475916632820825</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.225896173973403</v>
+        <v>0.410469877098012</v>
       </c>
       <c r="E11" t="n">
-        <v>0.769092836181488</v>
+        <v>1.49294127721565</v>
       </c>
       <c r="F11" t="n">
-        <v>0.458034241691245</v>
+        <v>0.163569156681941</v>
       </c>
       <c r="G11" t="n">
-        <v>0.79071601712743</v>
+        <v>0.475916632820825</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0936642672572645</v>
+        <v>-0.206612354243966</v>
       </c>
       <c r="E12" t="n">
-        <v>0.312020924850374</v>
+        <v>-0.700367570122216</v>
       </c>
       <c r="F12" t="n">
-        <v>0.76085929066789</v>
+        <v>0.498243766383061</v>
       </c>
       <c r="G12" t="n">
-        <v>0.978622775276868</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.468321336286322</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.75794432190218</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.106511536589313</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.79071601712743</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.239670330923</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.818759864872612</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.430304450443239</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.79071601712743</v>
+        <v>0.734159618041601</v>
       </c>
     </row>
   </sheetData>
@@ -2454,71 +2172,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.208791208791209</v>
+        <v>0.221978021978022</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2527,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.225896173973403</v>
+        <v>0.209367185633885</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,24 +2271,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.156734419398595</v>
+        <v>0.183224743803992</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.103296703296703</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,24 +2323,24 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.164835164835165</v>
+        <v>0.156043956043956</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -2631,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.265934065934066</v>
+        <v>0.23956043956044</v>
       </c>
     </row>
   </sheetData>
